--- a/Sindhi Muslim/Staff Attendance/Staff Attendance.xlsx
+++ b/Sindhi Muslim/Staff Attendance/Staff Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E6AF57-A663-42F1-968A-A38048F9C2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B41892-9F45-452E-AF01-E96A6F4451A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST-2024" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="46">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -184,7 +184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +226,22 @@
     <font>
       <b/>
       <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -524,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -580,6 +596,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -594,21 +625,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -628,80 +644,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="114">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="108">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -784,36 +749,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -829,396 +764,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1424,11 +969,11 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1439,16 +984,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1494,6 +1029,446 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1514,16 +1489,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1534,11 +1499,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2072,54 +2037,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="25"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="30"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="A3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="18" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Thu</v>
@@ -2244,13 +2209,13 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AI3" s="26" t="s">
+      <c r="AI3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="27"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="32"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2390,7 +2355,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -2411,7 +2376,7 @@
       <c r="M5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="O5" s="4" t="s">
@@ -2432,7 +2397,7 @@
       <c r="T5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U5" s="30" t="s">
+      <c r="U5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="V5" s="4" t="s">
@@ -2453,7 +2418,7 @@
       <c r="AA5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB5" s="30" t="s">
+      <c r="AB5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="AC5" s="33" t="s">
@@ -2513,7 +2478,7 @@
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="24"/>
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2532,7 +2497,7 @@
       <c r="M6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="31"/>
+      <c r="N6" s="24"/>
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2551,7 +2516,7 @@
       <c r="T6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U6" s="31"/>
+      <c r="U6" s="24"/>
       <c r="V6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2568,7 +2533,7 @@
       <c r="AA6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB6" s="31"/>
+      <c r="AB6" s="24"/>
       <c r="AC6" s="34"/>
       <c r="AD6" s="19" t="s">
         <v>6</v>
@@ -2622,7 +2587,7 @@
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2641,7 +2606,7 @@
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="31"/>
+      <c r="N7" s="24"/>
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2660,7 +2625,7 @@
       <c r="T7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U7" s="31"/>
+      <c r="U7" s="24"/>
       <c r="V7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2677,7 +2642,7 @@
       <c r="AA7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB7" s="31"/>
+      <c r="AB7" s="24"/>
       <c r="AC7" s="34"/>
       <c r="AD7" s="19" t="s">
         <v>6</v>
@@ -2731,7 +2696,7 @@
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2750,7 +2715,7 @@
       <c r="M8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N8" s="31"/>
+      <c r="N8" s="24"/>
       <c r="O8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2769,7 +2734,7 @@
       <c r="T8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U8" s="31"/>
+      <c r="U8" s="24"/>
       <c r="V8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2786,7 +2751,7 @@
       <c r="AA8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB8" s="31"/>
+      <c r="AB8" s="24"/>
       <c r="AC8" s="34"/>
       <c r="AD8" s="19" t="s">
         <v>6</v>
@@ -2840,7 +2805,7 @@
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2859,7 +2824,7 @@
       <c r="M9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="31"/>
+      <c r="N9" s="24"/>
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2878,7 +2843,7 @@
       <c r="T9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U9" s="31"/>
+      <c r="U9" s="24"/>
       <c r="V9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2895,7 +2860,7 @@
       <c r="AA9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB9" s="31"/>
+      <c r="AB9" s="24"/>
       <c r="AC9" s="34"/>
       <c r="AD9" s="19" t="s">
         <v>6</v>
@@ -2949,7 +2914,7 @@
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="31"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="4" t="s">
         <v>6</v>
       </c>
@@ -2968,7 +2933,7 @@
       <c r="M10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="31"/>
+      <c r="N10" s="24"/>
       <c r="O10" s="4" t="s">
         <v>6</v>
       </c>
@@ -2987,7 +2952,7 @@
       <c r="T10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U10" s="31"/>
+      <c r="U10" s="24"/>
       <c r="V10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3004,7 +2969,7 @@
       <c r="AA10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB10" s="31"/>
+      <c r="AB10" s="24"/>
       <c r="AC10" s="34"/>
       <c r="AD10" s="19" t="s">
         <v>6</v>
@@ -3058,7 +3023,7 @@
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3077,7 +3042,7 @@
       <c r="M11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="32"/>
+      <c r="N11" s="25"/>
       <c r="O11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3096,7 +3061,7 @@
       <c r="T11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U11" s="32"/>
+      <c r="U11" s="25"/>
       <c r="V11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3113,7 +3078,7 @@
       <c r="AA11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB11" s="32"/>
+      <c r="AB11" s="25"/>
       <c r="AC11" s="35"/>
       <c r="AD11" s="19" t="s">
         <v>6</v>
@@ -3150,54 +3115,54 @@
     </row>
     <row r="12" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
-      <c r="AI13" s="24"/>
-      <c r="AJ13" s="24"/>
-      <c r="AK13" s="24"/>
-      <c r="AL13" s="24"/>
-      <c r="AM13" s="25"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="30"/>
     </row>
     <row r="14" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
+      <c r="A14" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="18" t="str">
         <f>TEXT(D15,"ddd")</f>
         <v>Tue</v>
@@ -3322,13 +3287,13 @@
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="AI14" s="26" t="s">
+      <c r="AI14" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AJ14" s="26"/>
-      <c r="AK14" s="26"/>
-      <c r="AL14" s="26"/>
-      <c r="AM14" s="27"/>
+      <c r="AJ14" s="31"/>
+      <c r="AK14" s="31"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="32"/>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3469,7 +3434,7 @@
       <c r="F16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="23" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -3490,7 +3455,7 @@
       <c r="M16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N16" s="30" t="s">
+      <c r="N16" s="23" t="s">
         <v>29</v>
       </c>
       <c r="O16" s="4" t="s">
@@ -3511,7 +3476,7 @@
       <c r="T16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U16" s="30" t="s">
+      <c r="U16" s="23" t="s">
         <v>29</v>
       </c>
       <c r="V16" s="4" t="s">
@@ -3532,7 +3497,7 @@
       <c r="AA16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB16" s="30" t="s">
+      <c r="AB16" s="23" t="s">
         <v>29</v>
       </c>
       <c r="AC16" s="4" t="s">
@@ -3593,7 +3558,7 @@
       <c r="F17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3612,7 +3577,7 @@
       <c r="M17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N17" s="31"/>
+      <c r="N17" s="24"/>
       <c r="O17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3631,7 +3596,7 @@
       <c r="T17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U17" s="31"/>
+      <c r="U17" s="24"/>
       <c r="V17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3650,7 +3615,7 @@
       <c r="AA17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB17" s="31"/>
+      <c r="AB17" s="24"/>
       <c r="AC17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3709,7 +3674,7 @@
       <c r="F18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="31"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="4" t="s">
         <v>6</v>
       </c>
@@ -3728,7 +3693,7 @@
       <c r="M18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N18" s="31"/>
+      <c r="N18" s="24"/>
       <c r="O18" s="4" t="s">
         <v>6</v>
       </c>
@@ -3747,7 +3712,7 @@
       <c r="T18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U18" s="31"/>
+      <c r="U18" s="24"/>
       <c r="V18" s="4" t="s">
         <v>6</v>
       </c>
@@ -3766,7 +3731,7 @@
       <c r="AA18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB18" s="31"/>
+      <c r="AB18" s="24"/>
       <c r="AC18" s="4" t="s">
         <v>27</v>
       </c>
@@ -3825,7 +3790,7 @@
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="31"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="4" t="s">
         <v>6</v>
       </c>
@@ -3844,7 +3809,7 @@
       <c r="M19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N19" s="31"/>
+      <c r="N19" s="24"/>
       <c r="O19" s="4" t="s">
         <v>6</v>
       </c>
@@ -3863,7 +3828,7 @@
       <c r="T19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U19" s="31"/>
+      <c r="U19" s="24"/>
       <c r="V19" s="4" t="s">
         <v>6</v>
       </c>
@@ -3882,7 +3847,7 @@
       <c r="AA19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB19" s="31"/>
+      <c r="AB19" s="24"/>
       <c r="AC19" s="4" t="s">
         <v>27</v>
       </c>
@@ -3941,7 +3906,7 @@
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="31"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="4" t="s">
         <v>6</v>
       </c>
@@ -3960,7 +3925,7 @@
       <c r="M20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="31"/>
+      <c r="N20" s="24"/>
       <c r="O20" s="4" t="s">
         <v>6</v>
       </c>
@@ -3979,7 +3944,7 @@
       <c r="T20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U20" s="31"/>
+      <c r="U20" s="24"/>
       <c r="V20" s="4" t="s">
         <v>6</v>
       </c>
@@ -3998,7 +3963,7 @@
       <c r="AA20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB20" s="31"/>
+      <c r="AB20" s="24"/>
       <c r="AC20" s="4" t="s">
         <v>27</v>
       </c>
@@ -4056,7 +4021,7 @@
       <c r="F21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="13" t="s">
         <v>6</v>
       </c>
@@ -4075,7 +4040,7 @@
       <c r="M21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="31"/>
+      <c r="N21" s="24"/>
       <c r="O21" s="13" t="s">
         <v>6</v>
       </c>
@@ -4094,7 +4059,7 @@
       <c r="T21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="U21" s="31"/>
+      <c r="U21" s="24"/>
       <c r="V21" s="13" t="s">
         <v>6</v>
       </c>
@@ -4113,7 +4078,7 @@
       <c r="AA21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB21" s="31"/>
+      <c r="AB21" s="24"/>
       <c r="AC21" s="13" t="s">
         <v>27</v>
       </c>
@@ -4171,7 +4136,7 @@
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="32"/>
+      <c r="G22" s="25"/>
       <c r="H22" s="6" t="s">
         <v>6</v>
       </c>
@@ -4190,7 +4155,7 @@
       <c r="M22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="N22" s="32"/>
+      <c r="N22" s="25"/>
       <c r="O22" s="6" t="s">
         <v>6</v>
       </c>
@@ -4209,7 +4174,7 @@
       <c r="T22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="U22" s="32"/>
+      <c r="U22" s="25"/>
       <c r="V22" s="6" t="s">
         <v>6</v>
       </c>
@@ -4228,7 +4193,7 @@
       <c r="AA22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AB22" s="32"/>
+      <c r="AB22" s="25"/>
       <c r="AC22" s="6" t="s">
         <v>27</v>
       </c>
@@ -4270,11 +4235,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="G16:G22"/>
-    <mergeCell ref="N16:N22"/>
-    <mergeCell ref="U16:U22"/>
-    <mergeCell ref="AB16:AB22"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A2:AM2"/>
     <mergeCell ref="A13:AM13"/>
     <mergeCell ref="AI3:AM3"/>
@@ -4287,96 +4247,101 @@
     <mergeCell ref="W5:W11"/>
     <mergeCell ref="AC5:AC11"/>
     <mergeCell ref="AG5:AG11"/>
+    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="N16:N22"/>
+    <mergeCell ref="U16:U22"/>
+    <mergeCell ref="AB16:AB22"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <conditionalFormatting sqref="D16:F22 H16:M22 O16:T22">
-    <cfRule type="cellIs" dxfId="113" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="32" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="33" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:N5 U5:AC5 AG5 O5:T11 AD5:AF11 AH5:AH11 D6:F11 H6:M11 V6:V11 X6:AA11">
-    <cfRule type="cellIs" dxfId="111" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="35" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="36" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AH4 D5:N5 U5:AC5 AG5 O5:T11 AD5:AF11 AH5:AH11 D6:F11 H6:M11 V6:V11 X6:AA11">
-    <cfRule type="expression" dxfId="109" priority="34">
+    <cfRule type="expression" dxfId="103" priority="34">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:AH15 D16:F22 H16:M22 O16:T22">
-    <cfRule type="expression" dxfId="108" priority="31">
+    <cfRule type="expression" dxfId="102" priority="31">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16">
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>G$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="29" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="30" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16">
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>N$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="26" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U16">
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>U$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="24" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V16:AA22">
-    <cfRule type="expression" dxfId="98" priority="7">
+    <cfRule type="expression" dxfId="92" priority="7">
       <formula>V$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="8" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="9" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB16">
-    <cfRule type="expression" dxfId="95" priority="19">
+    <cfRule type="expression" dxfId="89" priority="19">
       <formula>AB$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="20" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="21" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC16:AH22">
-    <cfRule type="expression" dxfId="92" priority="1">
+    <cfRule type="expression" dxfId="86" priority="1">
       <formula>AC$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4401,53 +4366,53 @@
   <sheetData>
     <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:38" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
     </row>
     <row r="3" spans="1:38" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="A3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="18" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sun</v>
@@ -4568,13 +4533,13 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AH3" s="26" t="s">
+      <c r="AH3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="27"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="32"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -4702,7 +4667,7 @@
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -4723,7 +4688,7 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -4744,7 +4709,7 @@
       <c r="Q5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="30" t="s">
+      <c r="R5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="S5" s="4" t="s">
@@ -4765,7 +4730,7 @@
       <c r="X5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y5" s="30" t="s">
+      <c r="Y5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="Z5" s="4" t="s">
@@ -4786,7 +4751,7 @@
       <c r="AE5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF5" s="30" t="s">
+      <c r="AF5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="AG5" s="4" t="s">
@@ -4822,7 +4787,7 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="31"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4841,7 +4806,7 @@
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="31"/>
+      <c r="K6" s="24"/>
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4860,7 +4825,7 @@
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="31"/>
+      <c r="R6" s="24"/>
       <c r="S6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4879,7 +4844,7 @@
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="31"/>
+      <c r="Y6" s="24"/>
       <c r="Z6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4898,7 +4863,7 @@
       <c r="AE6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF6" s="31"/>
+      <c r="AF6" s="24"/>
       <c r="AG6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4933,7 +4898,7 @@
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="31"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4952,7 +4917,7 @@
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="24"/>
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4971,7 +4936,7 @@
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R7" s="31"/>
+      <c r="R7" s="24"/>
       <c r="S7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4990,7 +4955,7 @@
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y7" s="31"/>
+      <c r="Y7" s="24"/>
       <c r="Z7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5009,7 +4974,7 @@
       <c r="AE7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF7" s="31"/>
+      <c r="AF7" s="24"/>
       <c r="AG7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5044,7 +5009,7 @@
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="31"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5063,7 +5028,7 @@
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="31"/>
+      <c r="K8" s="24"/>
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5082,7 +5047,7 @@
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="31"/>
+      <c r="R8" s="24"/>
       <c r="S8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5101,7 +5066,7 @@
       <c r="X8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="31"/>
+      <c r="Y8" s="24"/>
       <c r="Z8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5120,7 +5085,7 @@
       <c r="AE8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF8" s="31"/>
+      <c r="AF8" s="24"/>
       <c r="AG8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5155,7 +5120,7 @@
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5174,7 +5139,7 @@
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="31"/>
+      <c r="K9" s="24"/>
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5193,7 +5158,7 @@
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="31"/>
+      <c r="R9" s="24"/>
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5212,7 +5177,7 @@
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y9" s="31"/>
+      <c r="Y9" s="24"/>
       <c r="Z9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5231,7 +5196,7 @@
       <c r="AE9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF9" s="31"/>
+      <c r="AF9" s="24"/>
       <c r="AG9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5266,7 +5231,7 @@
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5285,7 +5250,7 @@
       <c r="J10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="31"/>
+      <c r="K10" s="24"/>
       <c r="L10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5304,7 +5269,7 @@
       <c r="Q10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R10" s="31"/>
+      <c r="R10" s="24"/>
       <c r="S10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5323,7 +5288,7 @@
       <c r="X10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y10" s="31"/>
+      <c r="Y10" s="24"/>
       <c r="Z10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5342,7 +5307,7 @@
       <c r="AE10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF10" s="31"/>
+      <c r="AF10" s="24"/>
       <c r="AG10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5377,7 +5342,7 @@
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="31"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5396,7 +5361,7 @@
       <c r="J11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="31"/>
+      <c r="K11" s="24"/>
       <c r="L11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5415,7 +5380,7 @@
       <c r="Q11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R11" s="31"/>
+      <c r="R11" s="24"/>
       <c r="S11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5434,7 +5399,7 @@
       <c r="X11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y11" s="31"/>
+      <c r="Y11" s="24"/>
       <c r="Z11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5453,7 +5418,7 @@
       <c r="AE11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF11" s="31"/>
+      <c r="AF11" s="24"/>
       <c r="AG11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5591,53 +5556,53 @@
     </row>
     <row r="13" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:38" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
-      <c r="AI14" s="24"/>
-      <c r="AJ14" s="24"/>
-      <c r="AK14" s="24"/>
-      <c r="AL14" s="24"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="29"/>
     </row>
     <row r="15" spans="1:38" ht="27" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
+      <c r="A15" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
       <c r="D15" s="18" t="str">
         <f>TEXT(D16,"ddd")</f>
         <v>Tue</v>
@@ -5758,13 +5723,13 @@
         <f t="shared" si="6"/>
         <v>Wed</v>
       </c>
-      <c r="AH15" s="26" t="s">
+      <c r="AH15" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AI15" s="26"/>
-      <c r="AJ15" s="26"/>
-      <c r="AK15" s="26"/>
-      <c r="AL15" s="27"/>
+      <c r="AI15" s="31"/>
+      <c r="AJ15" s="31"/>
+      <c r="AK15" s="31"/>
+      <c r="AL15" s="32"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -5893,7 +5858,7 @@
       <c r="C17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="23" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="4" t="s">
@@ -5914,7 +5879,7 @@
       <c r="J17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="30" t="s">
+      <c r="K17" s="23" t="s">
         <v>29</v>
       </c>
       <c r="L17" s="4" t="s">
@@ -5935,7 +5900,7 @@
       <c r="Q17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R17" s="30" t="s">
+      <c r="R17" s="23" t="s">
         <v>29</v>
       </c>
       <c r="S17" s="4" t="s">
@@ -5956,7 +5921,7 @@
       <c r="X17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y17" s="30" t="s">
+      <c r="Y17" s="23" t="s">
         <v>29</v>
       </c>
       <c r="Z17" s="4" t="s">
@@ -5977,7 +5942,7 @@
       <c r="AE17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF17" s="30" t="s">
+      <c r="AF17" s="23" t="s">
         <v>29</v>
       </c>
       <c r="AG17" s="4" t="s">
@@ -6014,7 +5979,7 @@
       <c r="C18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="31"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="4" t="s">
         <v>6</v>
       </c>
@@ -6033,7 +5998,7 @@
       <c r="J18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K18" s="31"/>
+      <c r="K18" s="24"/>
       <c r="L18" s="4" t="s">
         <v>6</v>
       </c>
@@ -6052,7 +6017,7 @@
       <c r="Q18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R18" s="31"/>
+      <c r="R18" s="24"/>
       <c r="S18" s="4" t="s">
         <v>6</v>
       </c>
@@ -6071,7 +6036,7 @@
       <c r="X18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y18" s="31"/>
+      <c r="Y18" s="24"/>
       <c r="Z18" s="4" t="s">
         <v>6</v>
       </c>
@@ -6090,7 +6055,7 @@
       <c r="AE18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF18" s="31"/>
+      <c r="AF18" s="24"/>
       <c r="AG18" s="4" t="s">
         <v>6</v>
       </c>
@@ -6126,7 +6091,7 @@
       <c r="C19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="24"/>
       <c r="E19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6145,7 +6110,7 @@
       <c r="J19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K19" s="31"/>
+      <c r="K19" s="24"/>
       <c r="L19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6164,7 +6129,7 @@
       <c r="Q19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R19" s="31"/>
+      <c r="R19" s="24"/>
       <c r="S19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6183,7 +6148,7 @@
       <c r="X19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y19" s="31"/>
+      <c r="Y19" s="24"/>
       <c r="Z19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6202,7 +6167,7 @@
       <c r="AE19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF19" s="31"/>
+      <c r="AF19" s="24"/>
       <c r="AG19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6238,7 +6203,7 @@
       <c r="C20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="24"/>
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6257,7 +6222,7 @@
       <c r="J20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="31"/>
+      <c r="K20" s="24"/>
       <c r="L20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6276,7 +6241,7 @@
       <c r="Q20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R20" s="31"/>
+      <c r="R20" s="24"/>
       <c r="S20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6295,7 +6260,7 @@
       <c r="X20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y20" s="31"/>
+      <c r="Y20" s="24"/>
       <c r="Z20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6314,7 +6279,7 @@
       <c r="AE20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF20" s="31"/>
+      <c r="AF20" s="24"/>
       <c r="AG20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6350,7 +6315,7 @@
       <c r="C21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="31"/>
+      <c r="D21" s="24"/>
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6369,7 +6334,7 @@
       <c r="J21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="31"/>
+      <c r="K21" s="24"/>
       <c r="L21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6388,7 +6353,7 @@
       <c r="Q21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R21" s="31"/>
+      <c r="R21" s="24"/>
       <c r="S21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6407,7 +6372,7 @@
       <c r="X21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y21" s="31"/>
+      <c r="Y21" s="24"/>
       <c r="Z21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6426,7 +6391,7 @@
       <c r="AE21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AF21" s="31"/>
+      <c r="AF21" s="24"/>
       <c r="AG21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6461,7 +6426,7 @@
       <c r="C22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="31"/>
+      <c r="D22" s="24"/>
       <c r="E22" s="13" t="s">
         <v>6</v>
       </c>
@@ -6480,7 +6445,7 @@
       <c r="J22" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K22" s="31"/>
+      <c r="K22" s="24"/>
       <c r="L22" s="13" t="s">
         <v>6</v>
       </c>
@@ -6499,7 +6464,7 @@
       <c r="Q22" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="R22" s="31"/>
+      <c r="R22" s="24"/>
       <c r="S22" s="13" t="s">
         <v>6</v>
       </c>
@@ -6518,7 +6483,7 @@
       <c r="X22" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="Y22" s="31"/>
+      <c r="Y22" s="24"/>
       <c r="Z22" s="13" t="s">
         <v>6</v>
       </c>
@@ -6537,7 +6502,7 @@
       <c r="AE22" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AF22" s="31"/>
+      <c r="AF22" s="24"/>
       <c r="AG22" s="13" t="s">
         <v>6</v>
       </c>
@@ -6572,7 +6537,7 @@
       <c r="C23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="32"/>
+      <c r="D23" s="25"/>
       <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
@@ -6591,7 +6556,7 @@
       <c r="J23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K23" s="32"/>
+      <c r="K23" s="25"/>
       <c r="L23" s="6" t="s">
         <v>6</v>
       </c>
@@ -6610,7 +6575,7 @@
       <c r="Q23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="R23" s="32"/>
+      <c r="R23" s="25"/>
       <c r="S23" s="6" t="s">
         <v>6</v>
       </c>
@@ -6629,7 +6594,7 @@
       <c r="X23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="32"/>
+      <c r="Y23" s="25"/>
       <c r="Z23" s="6" t="s">
         <v>6</v>
       </c>
@@ -6648,7 +6613,7 @@
       <c r="AE23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AF23" s="32"/>
+      <c r="AF23" s="25"/>
       <c r="AG23" s="6" t="s">
         <v>7</v>
       </c>
@@ -6675,13 +6640,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="AH15:AL15"/>
-    <mergeCell ref="D17:D23"/>
-    <mergeCell ref="K17:K23"/>
-    <mergeCell ref="R17:R23"/>
-    <mergeCell ref="Y17:Y23"/>
-    <mergeCell ref="AF17:AF23"/>
     <mergeCell ref="A14:AL14"/>
     <mergeCell ref="R5:R12"/>
     <mergeCell ref="Y5:Y12"/>
@@ -6691,128 +6649,135 @@
     <mergeCell ref="AH3:AL3"/>
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="K5:K12"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="AH15:AL15"/>
+    <mergeCell ref="D17:D23"/>
+    <mergeCell ref="K17:K23"/>
+    <mergeCell ref="R17:R23"/>
+    <mergeCell ref="Y17:Y23"/>
+    <mergeCell ref="AF17:AF23"/>
   </mergeCells>
   <conditionalFormatting sqref="D17">
-    <cfRule type="cellIs" dxfId="89" priority="39" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="83" priority="37">
+      <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="38" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="37">
-      <formula>D$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="81" priority="39" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:F5 H5:M5 R5 X5:AA5 AF5 G5:G12 N5:Q12 S5:W12 AB5:AE12 AG5:AG12 E6:F12 H6:J12 L6:M12 X6:X12 Z6:AA12">
-    <cfRule type="cellIs" dxfId="86" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="65" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="66" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="65" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AG4 D5:F5 H5:M5 R5 X5:AA5 AF5 G5:G12 N5:Q12 S5:W12 AB5:AE12 AG5:AG12 E6:F12 H6:J12 L6:M12 X6:X12 Z6:AA12 D15:AG16">
-    <cfRule type="expression" dxfId="84" priority="64">
+    <cfRule type="expression" dxfId="78" priority="64">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17:J23">
-    <cfRule type="cellIs" dxfId="83" priority="23" operator="equal">
+    <cfRule type="expression" dxfId="77" priority="22">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="24" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="22">
-      <formula>E$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="cellIs" dxfId="80" priority="36" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="74" priority="34">
+      <formula>K$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="35" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="34">
-      <formula>K$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="72" priority="36" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17:Q23">
-    <cfRule type="expression" dxfId="77" priority="19">
+    <cfRule type="expression" dxfId="71" priority="19">
       <formula>L$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="20" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="21" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17">
-    <cfRule type="expression" dxfId="74" priority="28">
+    <cfRule type="expression" dxfId="68" priority="28">
       <formula>R$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="29" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="30" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S17:X23">
-    <cfRule type="expression" dxfId="71" priority="13">
+    <cfRule type="expression" dxfId="65" priority="13">
       <formula>S$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="14" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="15" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y17">
-    <cfRule type="expression" dxfId="68" priority="25">
+    <cfRule type="expression" dxfId="62" priority="25">
       <formula>Y$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="26" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z17:AE23">
-    <cfRule type="expression" dxfId="65" priority="4">
+    <cfRule type="expression" dxfId="59" priority="4">
       <formula>Z$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="6" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF17">
-    <cfRule type="cellIs" dxfId="62" priority="59" operator="equal">
+    <cfRule type="expression" dxfId="56" priority="58">
+      <formula>AF$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="59" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="60" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="58">
-      <formula>AF$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG17:AG23">
-    <cfRule type="cellIs" dxfId="59" priority="2" operator="equal">
+    <cfRule type="expression" dxfId="53" priority="1">
+      <formula>AG$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="1">
-      <formula>AG$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6838,54 +6803,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="25"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="30"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="A3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="18" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -7010,13 +6975,13 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="26" t="s">
+      <c r="AI3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="27"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="32"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -8190,54 +8155,54 @@
     </row>
     <row r="14" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="24"/>
-      <c r="AI15" s="24"/>
-      <c r="AJ15" s="24"/>
-      <c r="AK15" s="24"/>
-      <c r="AL15" s="24"/>
-      <c r="AM15" s="25"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="29"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="29"/>
+      <c r="AM15" s="30"/>
     </row>
     <row r="16" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
+      <c r="A16" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="18" t="str">
         <f>TEXT(D17,"ddd")</f>
         <v>Tue</v>
@@ -8362,13 +8327,13 @@
         <f t="shared" si="6"/>
         <v>Thu</v>
       </c>
-      <c r="AI16" s="26" t="s">
+      <c r="AI16" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="26"/>
-      <c r="AK16" s="26"/>
-      <c r="AL16" s="26"/>
-      <c r="AM16" s="27"/>
+      <c r="AJ16" s="31"/>
+      <c r="AK16" s="31"/>
+      <c r="AL16" s="31"/>
+      <c r="AM16" s="32"/>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -8515,7 +8480,7 @@
       <c r="H18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="I18" s="23" t="s">
         <v>29</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -8536,7 +8501,7 @@
       <c r="O18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P18" s="30" t="s">
+      <c r="P18" s="23" t="s">
         <v>29</v>
       </c>
       <c r="Q18" s="4" t="s">
@@ -8557,7 +8522,7 @@
       <c r="V18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W18" s="30" t="s">
+      <c r="W18" s="23" t="s">
         <v>29</v>
       </c>
       <c r="X18" s="4" t="s">
@@ -8578,7 +8543,7 @@
       <c r="AC18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD18" s="30" t="s">
+      <c r="AD18" s="23" t="s">
         <v>29</v>
       </c>
       <c r="AE18" s="4" t="s">
@@ -8639,7 +8604,7 @@
       <c r="H19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="31"/>
+      <c r="I19" s="24"/>
       <c r="J19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8658,7 +8623,7 @@
       <c r="O19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P19" s="31"/>
+      <c r="P19" s="24"/>
       <c r="Q19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8677,7 +8642,7 @@
       <c r="V19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W19" s="31"/>
+      <c r="W19" s="24"/>
       <c r="X19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8696,7 +8661,7 @@
       <c r="AC19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD19" s="31"/>
+      <c r="AD19" s="24"/>
       <c r="AE19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8756,7 +8721,7 @@
       <c r="H20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="31"/>
+      <c r="I20" s="24"/>
       <c r="J20" s="4" t="s">
         <v>6</v>
       </c>
@@ -8775,7 +8740,7 @@
       <c r="O20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P20" s="31"/>
+      <c r="P20" s="24"/>
       <c r="Q20" s="4" t="s">
         <v>6</v>
       </c>
@@ -8794,7 +8759,7 @@
       <c r="V20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W20" s="31"/>
+      <c r="W20" s="24"/>
       <c r="X20" s="4" t="s">
         <v>6</v>
       </c>
@@ -8813,7 +8778,7 @@
       <c r="AC20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD20" s="31"/>
+      <c r="AD20" s="24"/>
       <c r="AE20" s="4" t="s">
         <v>6</v>
       </c>
@@ -8873,7 +8838,7 @@
       <c r="H21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="31"/>
+      <c r="I21" s="24"/>
       <c r="J21" s="4" t="s">
         <v>6</v>
       </c>
@@ -8892,7 +8857,7 @@
       <c r="O21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P21" s="31"/>
+      <c r="P21" s="24"/>
       <c r="Q21" s="4" t="s">
         <v>27</v>
       </c>
@@ -8911,7 +8876,7 @@
       <c r="V21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="W21" s="31"/>
+      <c r="W21" s="24"/>
       <c r="X21" s="4" t="s">
         <v>27</v>
       </c>
@@ -8930,7 +8895,7 @@
       <c r="AC21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AD21" s="31"/>
+      <c r="AD21" s="24"/>
       <c r="AE21" s="4" t="s">
         <v>27</v>
       </c>
@@ -8990,7 +8955,7 @@
       <c r="H22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="31"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9009,7 +8974,7 @@
       <c r="O22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P22" s="31"/>
+      <c r="P22" s="24"/>
       <c r="Q22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9028,7 +8993,7 @@
       <c r="V22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W22" s="31"/>
+      <c r="W22" s="24"/>
       <c r="X22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9047,7 +9012,7 @@
       <c r="AC22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD22" s="31"/>
+      <c r="AD22" s="24"/>
       <c r="AE22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9106,7 +9071,7 @@
       <c r="H23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="31"/>
+      <c r="I23" s="24"/>
       <c r="J23" s="13" t="s">
         <v>6</v>
       </c>
@@ -9125,7 +9090,7 @@
       <c r="O23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="P23" s="31"/>
+      <c r="P23" s="24"/>
       <c r="Q23" s="13" t="s">
         <v>6</v>
       </c>
@@ -9144,7 +9109,7 @@
       <c r="V23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="W23" s="31"/>
+      <c r="W23" s="24"/>
       <c r="X23" s="13" t="s">
         <v>6</v>
       </c>
@@ -9163,7 +9128,7 @@
       <c r="AC23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AD23" s="31"/>
+      <c r="AD23" s="24"/>
       <c r="AE23" s="13" t="s">
         <v>6</v>
       </c>
@@ -9222,7 +9187,7 @@
       <c r="H24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="32"/>
+      <c r="I24" s="25"/>
       <c r="J24" s="6" t="s">
         <v>27</v>
       </c>
@@ -9241,7 +9206,7 @@
       <c r="O24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P24" s="32"/>
+      <c r="P24" s="25"/>
       <c r="Q24" s="6" t="s">
         <v>27</v>
       </c>
@@ -9260,7 +9225,7 @@
       <c r="V24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="W24" s="32"/>
+      <c r="W24" s="25"/>
       <c r="X24" s="6" t="s">
         <v>6</v>
       </c>
@@ -9279,7 +9244,7 @@
       <c r="AC24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD24" s="32"/>
+      <c r="AD24" s="25"/>
       <c r="AE24" s="6" t="s">
         <v>6</v>
       </c>
@@ -9331,115 +9296,115 @@
     <mergeCell ref="P5:P13"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:H24">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AH4 I5 P5 W5 AD5 D5:H13 J5:O13 Q5:V13 X5:AC13 AE5:AH13 D16:AH17">
-    <cfRule type="expression" dxfId="53" priority="85">
+    <cfRule type="expression" dxfId="47" priority="85">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5 P5 W5 AD5 D5:H13 J5:O13 Q5:V13 X5:AC13 AE5:AH13">
-    <cfRule type="cellIs" dxfId="52" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="86" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="87" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18">
-    <cfRule type="cellIs" dxfId="50" priority="39" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="37">
+    <cfRule type="expression" dxfId="44" priority="37">
       <formula>I$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="38" operator="equal">
       <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="39" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J18:O24">
-    <cfRule type="expression" dxfId="47" priority="25">
+    <cfRule type="expression" dxfId="41" priority="25">
       <formula>J$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="26" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18">
-    <cfRule type="cellIs" dxfId="44" priority="36" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="38" priority="34">
+      <formula>P$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="34">
-      <formula>P$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q18:V24">
-    <cfRule type="cellIs" dxfId="41" priority="24" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="22">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>Q$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="23" operator="equal">
       <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="24" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W18">
-    <cfRule type="expression" dxfId="38" priority="28">
+    <cfRule type="expression" dxfId="32" priority="28">
       <formula>W$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X18:AC24">
-    <cfRule type="expression" dxfId="35" priority="4">
+    <cfRule type="expression" dxfId="29" priority="4">
       <formula>X$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="6" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD18">
-    <cfRule type="expression" dxfId="32" priority="31">
+    <cfRule type="expression" dxfId="26" priority="31">
       <formula>AD$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="32" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="33" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="32" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE18:AH24">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>AE$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9449,7 +9414,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4ACDAB5-41AE-4980-8466-A5D7AD1F8A07}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9463,40 +9428,40 @@
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="25"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="30"/>
     </row>
     <row r="3" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="A3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="18" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Fri</v>
@@ -9565,13 +9530,13 @@
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="U3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="27"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="32"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -9666,7 +9631,7 @@
       <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -9687,7 +9652,7 @@
       <c r="L5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="30" t="s">
+      <c r="M5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="N5" s="4" t="s">
@@ -9708,7 +9673,7 @@
       <c r="S5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="30" t="s">
+      <c r="T5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="U5" s="4">
@@ -9747,7 +9712,7 @@
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="31"/>
+      <c r="F6" s="24"/>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
@@ -9764,7 +9729,7 @@
         <v>6</v>
       </c>
       <c r="L6" s="40"/>
-      <c r="M6" s="31"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="4" t="s">
         <v>6</v>
       </c>
@@ -9783,7 +9748,7 @@
       <c r="S6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="T6" s="31"/>
+      <c r="T6" s="24"/>
       <c r="U6" s="4">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -9820,7 +9785,7 @@
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="31"/>
+      <c r="F7" s="24"/>
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
@@ -9837,7 +9802,7 @@
         <v>6</v>
       </c>
       <c r="L7" s="40"/>
-      <c r="M7" s="31"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="4" t="s">
         <v>6</v>
       </c>
@@ -9856,7 +9821,7 @@
       <c r="S7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="31"/>
+      <c r="T7" s="24"/>
       <c r="U7" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -9893,7 +9858,7 @@
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="31"/>
+      <c r="F8" s="24"/>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
@@ -9910,7 +9875,7 @@
         <v>6</v>
       </c>
       <c r="L8" s="40"/>
-      <c r="M8" s="31"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="4" t="s">
         <v>6</v>
       </c>
@@ -9929,7 +9894,7 @@
       <c r="S8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="T8" s="31"/>
+      <c r="T8" s="24"/>
       <c r="U8" s="4">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -9966,7 +9931,7 @@
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="31"/>
+      <c r="F9" s="24"/>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
@@ -9983,7 +9948,7 @@
         <v>6</v>
       </c>
       <c r="L9" s="40"/>
-      <c r="M9" s="31"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="4" t="s">
         <v>6</v>
       </c>
@@ -10002,7 +9967,7 @@
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="31"/>
+      <c r="T9" s="24"/>
       <c r="U9" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -10039,7 +10004,7 @@
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="31"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
@@ -10056,7 +10021,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="40"/>
-      <c r="M10" s="31"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="4" t="s">
         <v>6</v>
       </c>
@@ -10075,7 +10040,7 @@
       <c r="S10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="31"/>
+      <c r="T10" s="24"/>
       <c r="U10" s="4">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -10112,7 +10077,7 @@
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="31"/>
+      <c r="F11" s="24"/>
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
@@ -10129,7 +10094,7 @@
         <v>6</v>
       </c>
       <c r="L11" s="40"/>
-      <c r="M11" s="31"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="4" t="s">
         <v>6</v>
       </c>
@@ -10148,7 +10113,7 @@
       <c r="S11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T11" s="31"/>
+      <c r="T11" s="24"/>
       <c r="U11" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -10185,7 +10150,7 @@
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="31"/>
+      <c r="F12" s="24"/>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
@@ -10202,7 +10167,7 @@
         <v>6</v>
       </c>
       <c r="L12" s="40"/>
-      <c r="M12" s="31"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="4" t="s">
         <v>6</v>
       </c>
@@ -10221,7 +10186,7 @@
       <c r="S12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T12" s="31"/>
+      <c r="T12" s="24"/>
       <c r="U12" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -10317,40 +10282,40 @@
     </row>
     <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="25"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="30"/>
     </row>
     <row r="17" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
+      <c r="A17" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
       <c r="D17" s="18" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Fri</v>
@@ -10419,13 +10384,13 @@
         <f t="shared" si="6"/>
         <v>Sun</v>
       </c>
-      <c r="U17" s="26" t="s">
+      <c r="U17" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="V17" s="26"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="27"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -10521,7 +10486,7 @@
       <c r="E19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="23" t="s">
         <v>29</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -10539,10 +10504,10 @@
       <c r="K19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="M19" s="30" t="s">
+      <c r="M19" s="23" t="s">
         <v>29</v>
       </c>
       <c r="N19" s="4" t="s">
@@ -10563,19 +10528,19 @@
       <c r="S19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T19" s="30" t="s">
+      <c r="T19" s="23" t="s">
         <v>29</v>
       </c>
       <c r="U19" s="8">
-        <f t="shared" ref="U19:U26" si="7">COUNTIF(D19:T19,"P")</f>
+        <f t="shared" ref="U19:U25" si="7">COUNTIF(D19:T19,"P")</f>
         <v>13</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" ref="V19:V26" si="8">COUNTIF(D19:T19,"A")</f>
+        <f t="shared" ref="V19:V25" si="8">COUNTIF(D19:T19,"A")</f>
         <v>0</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" ref="W19:W26" si="9">COUNTIF(D19:T19,"L")</f>
+        <f t="shared" ref="W19:W25" si="9">COUNTIF(D19:T19,"L")</f>
         <v>0</v>
       </c>
       <c r="X19" s="8">
@@ -10603,7 +10568,7 @@
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="31"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="4" t="s">
         <v>6</v>
       </c>
@@ -10619,8 +10584,8 @@
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="40"/>
-      <c r="M20" s="31"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="4" t="s">
         <v>6</v>
       </c>
@@ -10639,7 +10604,7 @@
       <c r="S20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T20" s="31"/>
+      <c r="T20" s="24"/>
       <c r="U20" s="8">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -10653,11 +10618,11 @@
         <v>0</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" ref="X20:X26" si="10">COUNTBLANK(D20:T20)</f>
+        <f t="shared" ref="X20:X25" si="10">COUNTBLANK(D20:T20)</f>
         <v>4</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" ref="Y20:Y26" si="11">U20+W20+X20</f>
+        <f t="shared" ref="Y20:Y25" si="11">U20+W20+X20</f>
         <v>17</v>
       </c>
     </row>
@@ -10678,7 +10643,7 @@
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="31"/>
+      <c r="F21" s="24"/>
       <c r="G21" s="4" t="s">
         <v>6</v>
       </c>
@@ -10694,8 +10659,8 @@
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="40"/>
-      <c r="M21" s="31"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="4" t="s">
         <v>6</v>
       </c>
@@ -10714,7 +10679,7 @@
       <c r="S21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="31"/>
+      <c r="T21" s="24"/>
       <c r="U21" s="8">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -10753,7 +10718,7 @@
       <c r="E22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="31"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="4" t="s">
         <v>6</v>
       </c>
@@ -10769,8 +10734,8 @@
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="40"/>
-      <c r="M22" s="31"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="4" t="s">
         <v>6</v>
       </c>
@@ -10789,7 +10754,7 @@
       <c r="S22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T22" s="31"/>
+      <c r="T22" s="24"/>
       <c r="U22" s="8">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -10828,7 +10793,7 @@
       <c r="E23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="31"/>
+      <c r="F23" s="24"/>
       <c r="G23" s="4" t="s">
         <v>6</v>
       </c>
@@ -10844,8 +10809,8 @@
       <c r="K23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="40"/>
-      <c r="M23" s="31"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="4" t="s">
         <v>6</v>
       </c>
@@ -10864,7 +10829,7 @@
       <c r="S23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="31"/>
+      <c r="T23" s="24"/>
       <c r="U23" s="8">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -10902,7 +10867,7 @@
       <c r="E24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="31"/>
+      <c r="F24" s="24"/>
       <c r="G24" s="4" t="s">
         <v>6</v>
       </c>
@@ -10918,8 +10883,8 @@
       <c r="K24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L24" s="40"/>
-      <c r="M24" s="31"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="4" t="s">
         <v>6</v>
       </c>
@@ -10938,7 +10903,7 @@
       <c r="S24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T24" s="31"/>
+      <c r="T24" s="24"/>
       <c r="U24" s="8">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -10960,150 +10925,76 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="25" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>7</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="E25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="F25" s="36"/>
+      <c r="G25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L25" s="40"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="4" t="s">
+      <c r="H25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="I25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="J25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="4" t="s">
+      <c r="K25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T25" s="31"/>
-      <c r="U25" s="8">
+      <c r="L25" s="44"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T25" s="36"/>
+      <c r="U25" s="9">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="V25" s="8">
+        <v>6</v>
+      </c>
+      <c r="V25" s="9">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W25" s="8">
+      <c r="W25" s="9">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X25" s="8">
+      <c r="X25" s="9">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="Y25" s="10">
-        <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
-        <v>7</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="36"/>
-      <c r="G26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="41"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="T26" s="36"/>
-      <c r="U26" s="9">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="10"/>
-        <v>4</v>
-      </c>
-      <c r="Y26" s="11">
+      <c r="Y25" s="11">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
@@ -11113,10 +11004,10 @@
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="A16:Y16"/>
     <mergeCell ref="L5:L13"/>
-    <mergeCell ref="T19:T26"/>
-    <mergeCell ref="M19:M26"/>
-    <mergeCell ref="F19:F26"/>
-    <mergeCell ref="L19:L26"/>
+    <mergeCell ref="T19:T25"/>
+    <mergeCell ref="M19:M25"/>
+    <mergeCell ref="F19:F25"/>
+    <mergeCell ref="L19:L25"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="U17:Y17"/>
     <mergeCell ref="A3:C3"/>
@@ -11126,95 +11017,73 @@
     <mergeCell ref="T5:T13"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:E13 I5:K13 G6:H13 N5:S13 D3:T4 D5:H5 L5:M5 T5 D17:T18">
-    <cfRule type="expression" dxfId="26" priority="90">
+    <cfRule type="expression" dxfId="20" priority="90">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="cellIs" dxfId="25" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="88" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="89" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="88" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:E25 G19:K25 N19:S25">
+    <cfRule type="expression" dxfId="17" priority="33">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="34" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19:E26">
-    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="35" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="34" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="33">
-      <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:H5 L5:M5 T5 I5:K13 N5:S13 D6:E13 G6:H13">
-    <cfRule type="cellIs" dxfId="20" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="91" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="92" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="91" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="cellIs" dxfId="18" priority="17" operator="equal">
+    <cfRule type="expression" dxfId="12" priority="16">
+      <formula>F$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>F$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:K13">
-    <cfRule type="cellIs" dxfId="15" priority="32" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="31" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19:K26">
-    <cfRule type="expression" dxfId="13" priority="10">
-      <formula>G$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:M19">
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
+    <cfRule type="expression" dxfId="7" priority="19">
+      <formula>L$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="19">
-      <formula>L$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:S13">
-    <cfRule type="cellIs" dxfId="7" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="29" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="30" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N19:S26">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>N$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19">
